--- a/Raw_Data/v7a_2050_yoll_Europe.xlsx
+++ b/Raw_Data/v7a_2050_yoll_Europe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35F4FF8-EAC7-4FB7-883C-9DC691ADE9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBAF52D-E716-4E78-BB87-11BB10E80D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2850" windowWidth="38640" windowHeight="21120" xr2:uid="{1150F6FC-3B38-460F-882C-1D2DB8B4BC66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{1150F6FC-3B38-460F-882C-1D2DB8B4BC66}"/>
   </bookViews>
   <sheets>
     <sheet name="yoll_Europe (11)" sheetId="12" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="yoll_Europe (3)" sheetId="5" r:id="rId9"/>
     <sheet name="yoll_Europe (2)" sheetId="4" r:id="rId10"/>
     <sheet name="yoll_Europe (1)" sheetId="3" r:id="rId11"/>
-    <sheet name="yoll_Europe" sheetId="1" r:id="rId12"/>
+    <sheet name="yoll_Europe (12)" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -34,9 +34,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="77">
   <si>
     <t>Premature mortality due to PM2.5</t>
-  </si>
-  <si>
-    <t>Scenario: LRTAP_Baseline_v7</t>
   </si>
   <si>
     <t xml:space="preserve">Region: </t>
@@ -262,6 +259,9 @@
   </si>
   <si>
     <t>Scenario: OPT Health -60 AAE -50 v7a</t>
+  </si>
+  <si>
+    <t>Scenario: Baseline_v7a</t>
   </si>
 </sst>
 </file>
@@ -1132,55 +1132,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -1255,10 +1255,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -1411,10 +1411,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -1619,10 +1619,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -1671,10 +1671,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -1928,10 +1928,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -1954,10 +1954,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -2110,10 +2110,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -2292,10 +2292,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -2422,10 +2422,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -2448,10 +2448,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -2538,55 +2538,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -2609,10 +2609,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -2661,10 +2661,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -2713,10 +2713,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -2843,10 +2843,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -2947,10 +2947,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -3025,10 +3025,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -3103,10 +3103,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -3880,10 +3880,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -3944,55 +3944,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -4015,10 +4015,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -4041,10 +4041,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -4093,10 +4093,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -4223,10 +4223,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -4249,10 +4249,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -4327,10 +4327,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -4405,10 +4405,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -4431,10 +4431,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -4457,10 +4457,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -4509,10 +4509,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -4613,10 +4613,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -4639,10 +4639,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -4818,10 +4818,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -4896,10 +4896,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -5000,10 +5000,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -5026,10 +5026,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -5078,10 +5078,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -5260,10 +5260,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -5312,7 +5312,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -5339,7 +5339,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC99E0B7-FD6A-4286-9EEE-008390387DA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D4B7701-FD46-401D-8D89-8238466E6928}">
   <dimension ref="A2:H61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -5350,107 +5350,107 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
       </c>
       <c r="D10">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="E10">
-        <v>36117</v>
+        <v>35990</v>
       </c>
       <c r="F10">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="G10">
-        <v>2950</v>
+        <v>2939</v>
       </c>
       <c r="H10">
-        <v>4099</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
       </c>
       <c r="D11">
-        <v>4.97</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="E11">
-        <v>57603</v>
+        <v>57225</v>
       </c>
       <c r="F11">
-        <v>4.18</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="G11">
-        <v>4914</v>
+        <v>4882</v>
       </c>
       <c r="H11">
-        <v>6311</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -5459,59 +5459,59 @@
         <v>5.19</v>
       </c>
       <c r="E12">
-        <v>40345</v>
+        <v>40294</v>
       </c>
       <c r="F12">
-        <v>4.9800000000000004</v>
+        <v>4.97</v>
       </c>
       <c r="G12">
-        <v>5091</v>
+        <v>5085</v>
       </c>
       <c r="H12">
-        <v>4143</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
       </c>
       <c r="D13">
-        <v>4.07</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E13">
-        <v>16701</v>
+        <v>16643</v>
       </c>
       <c r="F13">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="G13">
-        <v>1956</v>
+        <v>1949</v>
       </c>
       <c r="H13">
-        <v>1851</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
       </c>
       <c r="D14">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="E14">
-        <v>8158</v>
+        <v>8150</v>
       </c>
       <c r="F14">
         <v>5.27</v>
@@ -5520,41 +5520,41 @@
         <v>398</v>
       </c>
       <c r="H14">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
       </c>
       <c r="D15">
-        <v>4.1500000000000004</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="E15">
-        <v>45880</v>
+        <v>45750</v>
       </c>
       <c r="F15">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="G15">
-        <v>4123</v>
+        <v>4111</v>
       </c>
       <c r="H15">
-        <v>4841</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -5563,24 +5563,24 @@
         <v>3.13</v>
       </c>
       <c r="E16">
-        <v>17781</v>
+        <v>17741</v>
       </c>
       <c r="F16">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="G16">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="H16">
-        <v>1978</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -5589,7 +5589,7 @@
         <v>3.05</v>
       </c>
       <c r="E17">
-        <v>4642</v>
+        <v>4640</v>
       </c>
       <c r="F17">
         <v>2.97</v>
@@ -5603,10 +5603,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -5615,13 +5615,13 @@
         <v>2.36</v>
       </c>
       <c r="E18">
-        <v>12577</v>
+        <v>12571</v>
       </c>
       <c r="F18">
         <v>1.98</v>
       </c>
       <c r="G18">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H18">
         <v>1455</v>
@@ -5629,114 +5629,114 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
       </c>
       <c r="D19">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="E19">
-        <v>254702</v>
+        <v>253741</v>
       </c>
       <c r="F19">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="G19">
-        <v>20359</v>
+        <v>20282</v>
       </c>
       <c r="H19">
-        <v>27527</v>
+        <v>27423</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
       </c>
       <c r="D20">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="E20">
-        <v>345343</v>
+        <v>343621</v>
       </c>
       <c r="F20">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="G20">
-        <v>33295</v>
+        <v>33129</v>
       </c>
       <c r="H20">
-        <v>40047</v>
+        <v>39847</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
       </c>
       <c r="D21">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="E21">
-        <v>68076</v>
+        <v>67963</v>
       </c>
       <c r="F21">
-        <v>5.47</v>
+        <v>5.46</v>
       </c>
       <c r="G21">
-        <v>7052</v>
+        <v>7041</v>
       </c>
       <c r="H21">
-        <v>7320</v>
+        <v>7307</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
       </c>
       <c r="D22">
-        <v>4.74</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="E22">
-        <v>54322</v>
+        <v>54192</v>
       </c>
       <c r="F22">
-        <v>4.83</v>
+        <v>4.82</v>
       </c>
       <c r="G22">
-        <v>5553</v>
+        <v>5539</v>
       </c>
       <c r="H22">
-        <v>5236</v>
+        <v>5224</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -5745,7 +5745,7 @@
         <v>2.02</v>
       </c>
       <c r="E23">
-        <v>9744</v>
+        <v>9737</v>
       </c>
       <c r="F23">
         <v>1.62</v>
@@ -5754,41 +5754,41 @@
         <v>528</v>
       </c>
       <c r="H23">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
       </c>
       <c r="D24">
-        <v>6.03</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>341939</v>
+        <v>340262</v>
       </c>
       <c r="F24">
-        <v>4.8499999999999996</v>
+        <v>4.82</v>
       </c>
       <c r="G24">
-        <v>34948</v>
+        <v>34777</v>
       </c>
       <c r="H24">
-        <v>42083</v>
+        <v>41877</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -5797,24 +5797,24 @@
         <v>3.4</v>
       </c>
       <c r="E25">
-        <v>7849</v>
+        <v>7841</v>
       </c>
       <c r="F25">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="G25">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H25">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -5823,154 +5823,154 @@
         <v>3.54</v>
       </c>
       <c r="E26">
-        <v>12472</v>
+        <v>12458</v>
       </c>
       <c r="F26">
         <v>3.7</v>
       </c>
       <c r="G26">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H26">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
       </c>
       <c r="D27">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="E27">
-        <v>2554</v>
+        <v>2543</v>
       </c>
       <c r="F27">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="G27">
         <v>132</v>
       </c>
       <c r="H27">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
       </c>
       <c r="D28">
-        <v>7.05</v>
+        <v>7.03</v>
       </c>
       <c r="E28">
-        <v>4003</v>
+        <v>3992</v>
       </c>
       <c r="F28">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="G28">
         <v>193</v>
       </c>
       <c r="H28">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
       </c>
       <c r="D29">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="E29">
-        <v>87525</v>
+        <v>86986</v>
       </c>
       <c r="F29">
-        <v>4.2699999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="G29">
-        <v>6822</v>
+        <v>6780</v>
       </c>
       <c r="H29">
-        <v>10413</v>
+        <v>10349</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
       </c>
       <c r="D30">
-        <v>4.24</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="E30">
-        <v>188822</v>
+        <v>188469</v>
       </c>
       <c r="F30">
         <v>4.22</v>
       </c>
       <c r="G30">
-        <v>14443</v>
+        <v>14416</v>
       </c>
       <c r="H30">
-        <v>18319</v>
+        <v>18285</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
       </c>
       <c r="D31">
-        <v>4.0199999999999996</v>
+        <v>4.01</v>
       </c>
       <c r="E31">
-        <v>43067</v>
+        <v>42984</v>
       </c>
       <c r="F31">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="G31">
-        <v>3832</v>
+        <v>3825</v>
       </c>
       <c r="H31">
-        <v>4876</v>
+        <v>4866</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -5979,307 +5979,307 @@
         <v>5.47</v>
       </c>
       <c r="E32">
-        <v>118273</v>
+        <v>118164</v>
       </c>
       <c r="F32">
         <v>5.55</v>
       </c>
       <c r="G32">
-        <v>13056</v>
+        <v>13044</v>
       </c>
       <c r="H32">
-        <v>11958</v>
+        <v>11947</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
       </c>
       <c r="D33">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="E33">
-        <v>24871</v>
+        <v>24812</v>
       </c>
       <c r="F33">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="G33">
-        <v>1883</v>
+        <v>1878</v>
       </c>
       <c r="H33">
-        <v>2476</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
       </c>
       <c r="D34">
-        <v>4.92</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E34">
-        <v>11210</v>
+        <v>11168</v>
       </c>
       <c r="F34">
-        <v>4.2300000000000004</v>
+        <v>4.22</v>
       </c>
       <c r="G34">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="H34">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
       </c>
       <c r="D35">
-        <v>4.57</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="E35">
-        <v>217093</v>
+        <v>216342</v>
       </c>
       <c r="F35">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="G35">
-        <v>17220</v>
+        <v>17160</v>
       </c>
       <c r="H35">
-        <v>24621</v>
+        <v>24536</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
       </c>
       <c r="D36">
-        <v>2.48</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="E36">
-        <v>22543</v>
+        <v>22511</v>
       </c>
       <c r="F36">
         <v>1.92</v>
       </c>
       <c r="G36">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="H36">
-        <v>2596</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
       </c>
       <c r="D37">
-        <v>4.49</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="E37">
-        <v>2054211</v>
+        <v>2046791</v>
       </c>
       <c r="F37">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="G37">
-        <v>186792</v>
+        <v>186118</v>
       </c>
       <c r="H37">
-        <v>228238</v>
+        <v>227393</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
       </c>
       <c r="D38">
-        <v>9.0399999999999991</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="E38">
-        <v>23099</v>
+        <v>23070</v>
       </c>
       <c r="F38">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="G38">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="H38">
-        <v>2488</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
       </c>
       <c r="D39">
-        <v>24.52</v>
+        <v>24.57</v>
       </c>
       <c r="E39">
-        <v>76756</v>
+        <v>76895</v>
       </c>
       <c r="F39">
-        <v>26.32</v>
+        <v>26.37</v>
       </c>
       <c r="G39">
-        <v>6100</v>
+        <v>6111</v>
       </c>
       <c r="H39">
-        <v>7430</v>
+        <v>7443</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
       </c>
       <c r="D40">
-        <v>14.18</v>
+        <v>14.23</v>
       </c>
       <c r="E40">
-        <v>167291</v>
+        <v>167819</v>
       </c>
       <c r="F40">
-        <v>14.98</v>
+        <v>15.03</v>
       </c>
       <c r="G40">
-        <v>7441</v>
+        <v>7464</v>
       </c>
       <c r="H40">
-        <v>15141</v>
+        <v>15189</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
       </c>
       <c r="D41">
-        <v>6.73</v>
+        <v>6.72</v>
       </c>
       <c r="E41">
-        <v>78125</v>
+        <v>77973</v>
       </c>
       <c r="F41">
-        <v>7.36</v>
+        <v>7.34</v>
       </c>
       <c r="G41">
-        <v>7151</v>
+        <v>7137</v>
       </c>
       <c r="H41">
-        <v>7327</v>
+        <v>7313</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
       </c>
       <c r="D42">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
       <c r="E42">
-        <v>37277</v>
+        <v>37239</v>
       </c>
       <c r="F42">
-        <v>10.029999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="G42">
-        <v>3799</v>
+        <v>3795</v>
       </c>
       <c r="H42">
-        <v>3866</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
       </c>
       <c r="D43">
-        <v>10.97</v>
+        <v>10.94</v>
       </c>
       <c r="E43">
-        <v>50795</v>
+        <v>50650</v>
       </c>
       <c r="F43">
-        <v>10.94</v>
+        <v>10.91</v>
       </c>
       <c r="G43">
-        <v>4552</v>
+        <v>4539</v>
       </c>
       <c r="H43">
-        <v>4519</v>
+        <v>4506</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -6302,36 +6302,36 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
       </c>
       <c r="D45">
-        <v>21.91</v>
+        <v>21.43</v>
       </c>
       <c r="E45">
-        <v>535333</v>
+        <v>523798</v>
       </c>
       <c r="F45">
-        <v>24.18</v>
+        <v>23.66</v>
       </c>
       <c r="G45">
-        <v>24271</v>
+        <v>23748</v>
       </c>
       <c r="H45">
-        <v>42188</v>
+        <v>41279</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -6340,50 +6340,50 @@
         <v>14.78</v>
       </c>
       <c r="E46">
-        <v>22443</v>
+        <v>22432</v>
       </c>
       <c r="F46">
-        <v>13.87</v>
+        <v>13.86</v>
       </c>
       <c r="G46">
         <v>1250</v>
       </c>
       <c r="H46">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
       </c>
       <c r="D47">
-        <v>15.86</v>
+        <v>15.95</v>
       </c>
       <c r="E47">
-        <v>129550</v>
+        <v>130224</v>
       </c>
       <c r="F47">
-        <v>16.97</v>
+        <v>17.05</v>
       </c>
       <c r="G47">
-        <v>5515</v>
+        <v>5544</v>
       </c>
       <c r="H47">
-        <v>10063</v>
+        <v>10116</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -6392,76 +6392,76 @@
         <v>8.68</v>
       </c>
       <c r="E48">
-        <v>16422</v>
+        <v>16409</v>
       </c>
       <c r="F48">
-        <v>8.15</v>
+        <v>8.14</v>
       </c>
       <c r="G48">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H48">
-        <v>1761</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
       </c>
       <c r="D49">
-        <v>8.5</v>
+        <v>8.51</v>
       </c>
       <c r="E49">
-        <v>32341</v>
+        <v>32378</v>
       </c>
       <c r="F49">
-        <v>9.0299999999999994</v>
+        <v>9.0399999999999991</v>
       </c>
       <c r="G49">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="H49">
-        <v>2896</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
       </c>
       <c r="D50">
-        <v>10.23</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="E50">
-        <v>6847</v>
+        <v>6841</v>
       </c>
       <c r="F50">
-        <v>9.65</v>
+        <v>9.64</v>
       </c>
       <c r="G50">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H50">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -6470,154 +6470,154 @@
         <v>2.37</v>
       </c>
       <c r="E51">
-        <v>11663</v>
+        <v>11648</v>
       </c>
       <c r="F51">
         <v>1.85</v>
       </c>
       <c r="G51">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H51">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
       </c>
       <c r="D52">
-        <v>9.1199999999999992</v>
+        <v>9.16</v>
       </c>
       <c r="E52">
-        <v>1407182</v>
+        <v>1413098</v>
       </c>
       <c r="F52">
-        <v>10.15</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G52">
-        <v>109692</v>
+        <v>110153</v>
       </c>
       <c r="H52">
-        <v>115840</v>
+        <v>116327</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
       </c>
       <c r="D53">
-        <v>8.3800000000000008</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="E53">
-        <v>65843</v>
+        <v>65773</v>
       </c>
       <c r="F53">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="G53">
-        <v>7460</v>
+        <v>7452</v>
       </c>
       <c r="H53">
-        <v>6509</v>
+        <v>6502</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
       </c>
       <c r="D54">
-        <v>4.38</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E54">
-        <v>36042</v>
+        <v>35814</v>
       </c>
       <c r="F54">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="G54">
-        <v>2651</v>
+        <v>2635</v>
       </c>
       <c r="H54">
-        <v>4221</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
       </c>
       <c r="D55">
-        <v>20.56</v>
+        <v>20.63</v>
       </c>
       <c r="E55">
-        <v>218843</v>
+        <v>219545</v>
       </c>
       <c r="F55">
-        <v>22.86</v>
+        <v>22.93</v>
       </c>
       <c r="G55">
-        <v>5998</v>
+        <v>6017</v>
       </c>
       <c r="H55">
-        <v>16396</v>
+        <v>16448</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
       </c>
       <c r="D56">
-        <v>14.19</v>
+        <v>14.2</v>
       </c>
       <c r="E56">
-        <v>133130</v>
+        <v>133236</v>
       </c>
       <c r="F56">
-        <v>16.02</v>
+        <v>16.03</v>
       </c>
       <c r="G56">
-        <v>3667</v>
+        <v>3670</v>
       </c>
       <c r="H56">
-        <v>10546</v>
+        <v>10555</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -6626,117 +6626,117 @@
         <v>11.99</v>
       </c>
       <c r="E57">
-        <v>1038228</v>
+        <v>1038098</v>
       </c>
       <c r="F57">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
       <c r="G57">
-        <v>46467</v>
+        <v>46461</v>
       </c>
       <c r="H57">
-        <v>94468</v>
+        <v>94456</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
       </c>
       <c r="D58">
-        <v>8.8699999999999992</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="E58">
-        <v>520714</v>
+        <v>521471</v>
       </c>
       <c r="F58">
-        <v>9.49</v>
+        <v>9.5</v>
       </c>
       <c r="G58">
-        <v>46494</v>
+        <v>46562</v>
       </c>
       <c r="H58">
-        <v>42689</v>
+        <v>42752</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="E59">
-        <v>278424</v>
+        <v>277717</v>
       </c>
       <c r="F59">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="G59">
-        <v>21535</v>
+        <v>21480</v>
       </c>
       <c r="H59">
-        <v>28868</v>
+        <v>28794</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
       </c>
       <c r="D60">
-        <v>12.8</v>
+        <v>12.85</v>
       </c>
       <c r="E60">
-        <v>549069</v>
+        <v>551284</v>
       </c>
       <c r="F60">
-        <v>14.33</v>
+        <v>14.38</v>
       </c>
       <c r="G60">
-        <v>18331</v>
+        <v>18405</v>
       </c>
       <c r="H60">
-        <v>41946</v>
+        <v>42115</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
       </c>
       <c r="D61">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="E61">
-        <v>5436463</v>
+        <v>5434460</v>
       </c>
       <c r="F61">
         <v>10.45</v>
       </c>
       <c r="G61">
-        <v>330231</v>
+        <v>330278</v>
       </c>
       <c r="H61">
-        <v>463436</v>
+        <v>463266</v>
       </c>
     </row>
   </sheetData>
@@ -6756,55 +6756,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -6827,10 +6827,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -6853,10 +6853,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -6879,10 +6879,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -6905,10 +6905,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -6957,10 +6957,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -7009,10 +7009,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -7035,10 +7035,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -7061,10 +7061,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -7139,10 +7139,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -7165,10 +7165,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -7191,10 +7191,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -7217,10 +7217,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -7243,10 +7243,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -7269,10 +7269,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -7295,10 +7295,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -7347,10 +7347,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -7373,10 +7373,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -7451,10 +7451,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -7477,10 +7477,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -7526,10 +7526,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -7552,10 +7552,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -7604,10 +7604,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -7630,10 +7630,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -7656,10 +7656,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -7682,10 +7682,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -7708,10 +7708,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -7760,10 +7760,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -7786,10 +7786,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -7812,10 +7812,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -7838,10 +7838,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -7864,10 +7864,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -7890,10 +7890,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -7916,10 +7916,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -7942,10 +7942,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -7968,10 +7968,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -7994,10 +7994,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -8020,10 +8020,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -8046,10 +8046,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -8098,10 +8098,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -8124,7 +8124,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -8162,55 +8162,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -8233,10 +8233,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -8259,10 +8259,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -8285,10 +8285,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -8337,10 +8337,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -8363,10 +8363,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -8389,10 +8389,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -8415,10 +8415,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -8467,10 +8467,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -8493,10 +8493,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -8519,10 +8519,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -8545,10 +8545,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -8571,10 +8571,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -8623,10 +8623,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -8649,10 +8649,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -8675,10 +8675,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -8753,10 +8753,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -8779,10 +8779,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -8857,10 +8857,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -8909,7 +8909,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -8932,10 +8932,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -8984,10 +8984,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -9036,10 +9036,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -9088,10 +9088,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -9140,10 +9140,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -9166,10 +9166,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -9192,10 +9192,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -9218,10 +9218,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -9244,10 +9244,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -9270,10 +9270,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -9296,10 +9296,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -9322,10 +9322,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -9348,10 +9348,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -9400,10 +9400,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -9426,10 +9426,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -9478,10 +9478,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -9504,10 +9504,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -9568,55 +9568,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -9639,10 +9639,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -9743,10 +9743,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -9795,10 +9795,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -9821,10 +9821,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -9847,10 +9847,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -9873,10 +9873,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -9899,10 +9899,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -9925,10 +9925,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -9977,10 +9977,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -10003,10 +10003,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -10029,10 +10029,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -10055,10 +10055,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -10081,10 +10081,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -10159,10 +10159,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -10185,10 +10185,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -10211,10 +10211,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -10237,10 +10237,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -10263,10 +10263,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -10289,10 +10289,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -10315,7 +10315,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -10338,10 +10338,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -10390,10 +10390,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -10416,10 +10416,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -10442,10 +10442,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -10468,10 +10468,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -10494,10 +10494,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -10520,10 +10520,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -10546,10 +10546,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -10572,10 +10572,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -10598,10 +10598,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -10624,10 +10624,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -10676,10 +10676,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -10702,10 +10702,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -10754,10 +10754,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -10780,10 +10780,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -10806,10 +10806,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -10832,10 +10832,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -10858,10 +10858,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -10884,10 +10884,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -10910,10 +10910,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -10936,7 +10936,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -10974,55 +10974,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -11045,10 +11045,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -11071,10 +11071,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -11097,10 +11097,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -11123,10 +11123,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -11149,10 +11149,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -11175,10 +11175,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -11201,10 +11201,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -11227,10 +11227,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -11279,10 +11279,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -11305,10 +11305,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -11357,10 +11357,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -11383,10 +11383,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -11409,10 +11409,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -11461,10 +11461,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -11487,10 +11487,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -11513,10 +11513,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -11539,10 +11539,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -11565,10 +11565,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -11591,10 +11591,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -11617,10 +11617,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -11643,10 +11643,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -11669,10 +11669,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -11695,10 +11695,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -11721,7 +11721,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -11744,10 +11744,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -11770,10 +11770,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -11796,10 +11796,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -11822,10 +11822,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -11848,10 +11848,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -11874,10 +11874,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -11900,10 +11900,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -11926,10 +11926,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -11952,10 +11952,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -11978,10 +11978,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -12004,10 +12004,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -12030,10 +12030,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -12056,10 +12056,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -12082,10 +12082,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -12108,10 +12108,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -12160,10 +12160,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -12186,10 +12186,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -12212,10 +12212,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -12238,10 +12238,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -12290,10 +12290,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -12316,10 +12316,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -12342,7 +12342,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -12380,55 +12380,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -12451,10 +12451,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -12477,10 +12477,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -12503,10 +12503,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -12529,10 +12529,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -12555,10 +12555,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -12581,10 +12581,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -12633,10 +12633,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -12659,10 +12659,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -12711,10 +12711,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -12737,10 +12737,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -12763,10 +12763,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -12789,10 +12789,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -12815,10 +12815,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -12841,10 +12841,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -12867,10 +12867,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -12893,10 +12893,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -12945,10 +12945,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -12971,10 +12971,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -12997,10 +12997,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -13023,10 +13023,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -13049,10 +13049,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -13075,10 +13075,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -13101,10 +13101,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -13127,7 +13127,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -13150,10 +13150,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -13176,10 +13176,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -13202,10 +13202,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -13228,10 +13228,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -13254,10 +13254,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -13280,10 +13280,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -13306,10 +13306,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -13332,10 +13332,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -13358,10 +13358,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -13410,10 +13410,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -13462,10 +13462,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -13488,10 +13488,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -13514,10 +13514,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -13540,10 +13540,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -13566,10 +13566,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -13618,10 +13618,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -13644,10 +13644,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -13670,10 +13670,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -13696,10 +13696,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -13722,10 +13722,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -13748,7 +13748,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -13786,55 +13786,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -13857,10 +13857,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -13909,10 +13909,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -13935,10 +13935,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -13961,10 +13961,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -13987,10 +13987,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -14013,10 +14013,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -14039,10 +14039,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -14065,10 +14065,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -14091,10 +14091,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -14117,10 +14117,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -14143,10 +14143,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -14169,10 +14169,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -14195,10 +14195,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -14221,10 +14221,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -14247,10 +14247,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -14273,10 +14273,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -14299,10 +14299,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -14325,10 +14325,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -14351,10 +14351,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -14377,10 +14377,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -14403,10 +14403,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -14429,10 +14429,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -14455,10 +14455,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -14481,10 +14481,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -14507,10 +14507,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -14533,7 +14533,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -14556,10 +14556,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -14582,10 +14582,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -14608,10 +14608,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -14634,10 +14634,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -14660,10 +14660,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -14686,10 +14686,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -14712,10 +14712,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -14738,10 +14738,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -14764,10 +14764,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -14790,10 +14790,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -14816,10 +14816,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -14842,10 +14842,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -14868,10 +14868,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -14894,10 +14894,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -14920,10 +14920,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -14946,10 +14946,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -14972,10 +14972,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -14998,10 +14998,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -15024,10 +15024,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -15050,10 +15050,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -15076,10 +15076,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -15102,10 +15102,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -15128,10 +15128,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -15192,55 +15192,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -15263,10 +15263,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -15289,10 +15289,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -15315,10 +15315,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -15341,10 +15341,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -15367,10 +15367,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -15393,10 +15393,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -15419,10 +15419,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -15445,10 +15445,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -15471,10 +15471,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -15497,10 +15497,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -15523,10 +15523,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -15549,10 +15549,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -15575,10 +15575,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -15601,10 +15601,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -15627,10 +15627,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -15653,10 +15653,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -15679,10 +15679,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -15705,10 +15705,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -15731,10 +15731,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -15757,10 +15757,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -15809,10 +15809,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -15835,10 +15835,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -15861,10 +15861,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -15887,10 +15887,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -15913,10 +15913,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -15988,10 +15988,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -16014,10 +16014,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -16066,10 +16066,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -16092,10 +16092,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -16118,10 +16118,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -16144,10 +16144,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -16170,10 +16170,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -16196,10 +16196,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -16222,10 +16222,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -16248,10 +16248,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -16274,10 +16274,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -16300,10 +16300,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -16326,10 +16326,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -16352,10 +16352,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -16378,10 +16378,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -16404,10 +16404,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -16430,10 +16430,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -16456,10 +16456,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -16482,10 +16482,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -16508,10 +16508,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -16534,10 +16534,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -16560,7 +16560,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>
@@ -16598,55 +16598,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.7200000000000006</v>
@@ -16669,10 +16669,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.87</v>
@@ -16695,10 +16695,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.4</v>
@@ -16721,10 +16721,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.23</v>
@@ -16747,10 +16747,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.51</v>
@@ -16773,10 +16773,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>9.83</v>
@@ -16799,10 +16799,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -16825,10 +16825,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.17</v>
@@ -16851,10 +16851,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.35</v>
@@ -16877,10 +16877,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>68.22</v>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>78.3</v>
@@ -16929,10 +16929,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>8.81</v>
@@ -16955,10 +16955,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>8.7200000000000006</v>
@@ -16981,10 +16981,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.97</v>
@@ -17007,10 +17007,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>51.89</v>
@@ -17033,10 +17033,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.51</v>
@@ -17059,10 +17059,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.2599999999999998</v>
@@ -17085,10 +17085,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.79</v>
@@ -17111,10 +17111,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.54</v>
@@ -17137,10 +17137,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>18.96</v>
@@ -17163,10 +17163,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>32.81</v>
@@ -17189,10 +17189,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>9.77</v>
@@ -17215,10 +17215,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>16.03</v>
@@ -17241,10 +17241,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>4.9400000000000004</v>
@@ -17267,10 +17267,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>1.98</v>
@@ -17293,10 +17293,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>44.93</v>
@@ -17319,10 +17319,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.31</v>
@@ -17345,7 +17345,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>420.96</v>
@@ -17368,10 +17368,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.2400000000000002</v>
@@ -17394,10 +17394,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.5</v>
@@ -17420,10 +17420,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.22</v>
@@ -17446,10 +17446,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>7.45</v>
@@ -17472,10 +17472,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.46</v>
@@ -17498,10 +17498,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.66</v>
@@ -17524,10 +17524,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -17550,10 +17550,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>26.54</v>
@@ -17576,10 +17576,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.64</v>
@@ -17602,10 +17602,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>9.64</v>
@@ -17628,10 +17628,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.51</v>
@@ -17654,10 +17654,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.35</v>
@@ -17680,10 +17680,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.53</v>
@@ -17706,10 +17706,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.9</v>
@@ -17732,10 +17732,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>100.05</v>
@@ -17758,10 +17758,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.53</v>
@@ -17784,10 +17784,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.34</v>
@@ -17810,10 +17810,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>15.57</v>
@@ -17836,10 +17836,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>9.64</v>
@@ -17862,10 +17862,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.26</v>
@@ -17888,10 +17888,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>31.99</v>
@@ -17914,10 +17914,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>75.5</v>
@@ -17940,10 +17940,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>52.21</v>
@@ -17966,7 +17966,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>469.2</v>

--- a/Raw_Data/v7a_2050_yoll_Europe.xlsx
+++ b/Raw_Data/v7a_2050_yoll_Europe.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBAF52D-E716-4E78-BB87-11BB10E80D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{1150F6FC-3B38-460F-882C-1D2DB8B4BC66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="11" xr2:uid="{1150F6FC-3B38-460F-882C-1D2DB8B4BC66}"/>
   </bookViews>
   <sheets>
     <sheet name="yoll_Europe (11)" sheetId="12" r:id="rId1"/>
